--- a/lojas-proprias/pwr_reports_mensal/KEYS Service Main Service Exceptions - Lojas Corporativas (Stores)(2026-09-01 - 2026-09-06).xlsx
+++ b/lojas-proprias/pwr_reports_mensal/KEYS Service Main Service Exceptions - Lojas Corporativas (Stores)(2026-09-01 - 2026-09-06).xlsx
@@ -227,34 +227,34 @@
     <t>22</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>R$ 52.474,28</t>
-  </si>
-  <si>
-    <t>572.8</t>
-  </si>
-  <si>
-    <t>395.8</t>
-  </si>
-  <si>
-    <t>6.47</t>
-  </si>
-  <si>
-    <t>17.6</t>
-  </si>
-  <si>
-    <t>4.1</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>R$ 53.177,21</t>
+  </si>
+  <si>
+    <t>580.0</t>
+  </si>
+  <si>
+    <t>417.8</t>
+  </si>
+  <si>
+    <t>6.48</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>4.2</t>
   </si>
   <si>
     <t>6.2</t>
   </si>
   <si>
-    <t>45.4%</t>
-  </si>
-  <si>
-    <t>13.8%</t>
+    <t>43.3%</t>
+  </si>
+  <si>
+    <t>13.5%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -272,19 +272,19 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>5.2%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
   </si>
   <si>
     <t>4.4%</t>
   </si>
   <si>
-    <t>1247.0</t>
-  </si>
-  <si>
-    <t>1089.0</t>
+    <t>1289.0</t>
+  </si>
+  <si>
+    <t>1127.0</t>
   </si>
   <si>
     <t>19.0</t>
@@ -293,25 +293,25 @@
     <t>3.0</t>
   </si>
   <si>
-    <t>93.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>22.0</t>
-  </si>
-  <si>
-    <t>413.0</t>
-  </si>
-  <si>
-    <t>198.0</t>
-  </si>
-  <si>
-    <t>352.0</t>
-  </si>
-  <si>
-    <t>1.5%</t>
+    <t>99.0</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>23.0</t>
+  </si>
+  <si>
+    <t>426.0</t>
+  </si>
+  <si>
+    <t>203.0</t>
+  </si>
+  <si>
+    <t>368.0</t>
+  </si>
+  <si>
+    <t>1.4%</t>
   </si>
   <si>
     <t>121.0</t>
@@ -1286,7 +1286,7 @@
         <v>597</v>
       </c>
       <c r="O4" s="6">
-        <v>148</v>
+        <v>459</v>
       </c>
       <c r="P4" s="7">
         <v>7.963713798977853</v>
@@ -1304,7 +1304,7 @@
         <v>0.43013100436681223</v>
       </c>
       <c r="U4" s="9">
-        <v>0.11486486486486487</v>
+        <v>0.076252723311546838</v>
       </c>
       <c r="V4" s="9">
         <v>0</v>
@@ -1313,52 +1313,52 @@
         <v>0</v>
       </c>
       <c r="X4" s="9">
-        <v>0.013513513513513514</v>
+        <v>0.013071895424836602</v>
       </c>
       <c r="Y4" s="9">
-        <v>0</v>
+        <v>0.0021786492374727671</v>
       </c>
       <c r="Z4" s="9">
-        <v>0.013513513513513514</v>
+        <v>0.0065359477124183009</v>
       </c>
       <c r="AA4" s="9">
-        <v>0.060810810810810814</v>
+        <v>0.037037037037037035</v>
       </c>
       <c r="AB4" s="9">
-        <v>0.013513513513513514</v>
+        <v>0.0087145969498910684</v>
       </c>
       <c r="AC4" s="9">
-        <v>0.027027027027027029</v>
+        <v>0.017429193899782137</v>
       </c>
       <c r="AD4" s="6">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="AE4" s="6">
+        <v>35</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI4" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="6">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="6">
         <v>17</v>
       </c>
-      <c r="AF4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="6">
-        <v>2</v>
-      </c>
-      <c r="AI4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="6">
-        <v>2</v>
-      </c>
-      <c r="AK4" s="6">
-        <v>9</v>
-      </c>
       <c r="AL4" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM4" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AN4" s="9">
         <v>0</v>
@@ -3474,7 +3474,7 @@
         <v>19714</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C19" s="4">
         <v>51</v>
@@ -3505,61 +3505,61 @@
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="5">
-        <v>43590.399999999994</v>
+        <v>58351.899999999994</v>
       </c>
       <c r="N19" s="6">
-        <v>444</v>
+        <v>594</v>
       </c>
       <c r="O19" s="6">
-        <v>322</v>
+        <v>451</v>
       </c>
       <c r="P19" s="7">
-        <v>6.84249592760181</v>
+        <v>7.0879907407407403</v>
       </c>
       <c r="Q19" s="8">
-        <v>17.638437187499999</v>
+        <v>18.563288641425391</v>
       </c>
       <c r="R19" s="8">
-        <v>3.6658779179810725</v>
+        <v>4.4033180995475112</v>
       </c>
       <c r="S19" s="8">
         <v>7</v>
       </c>
       <c r="T19" s="9">
-        <v>0.48749999999999999</v>
+        <v>0.41202672605790647</v>
       </c>
       <c r="U19" s="9">
-        <v>0.083850931677018639</v>
+        <v>0.10421286031042129</v>
       </c>
       <c r="V19" s="9">
-        <v>0.009316770186335404</v>
+        <v>0.0066518847006651885</v>
       </c>
       <c r="W19" s="9">
         <v>0</v>
       </c>
       <c r="X19" s="9">
-        <v>0.012422360248447204</v>
+        <v>0.013303769401330377</v>
       </c>
       <c r="Y19" s="9">
         <v>0</v>
       </c>
       <c r="Z19" s="9">
-        <v>0.003105590062111801</v>
+        <v>0.0022172949002217295</v>
       </c>
       <c r="AA19" s="9">
-        <v>0.027950310559006212</v>
+        <v>0.031042128603104215</v>
       </c>
       <c r="AB19" s="9">
-        <v>0.018633540372670808</v>
+        <v>0.019955654101995565</v>
       </c>
       <c r="AC19" s="9">
-        <v>0.018633540372670808</v>
+        <v>0.039911308203991129</v>
       </c>
       <c r="AD19" s="6">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="AE19" s="6">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="AF19" s="6">
         <v>3</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI19" s="6">
         <v>0</v>
@@ -3577,13 +3577,13 @@
         <v>1</v>
       </c>
       <c r="AK19" s="6">
+        <v>14</v>
+      </c>
+      <c r="AL19" s="6">
         <v>9</v>
       </c>
-      <c r="AL19" s="6">
-        <v>6</v>
-      </c>
       <c r="AM19" s="6">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
